--- a/public/sample/거래명세서_한울전자_2026상반기.xlsx
+++ b/public/sample/거래명세서_한울전자_2026상반기.xlsx
@@ -37,7 +37,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>납품 후 45일</t>
+          <t>검수 완료 후 익월 15일</t>
         </is>
       </c>
     </row>
@@ -60,6 +60,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>단가</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>공급가액</t>
         </is>
       </c>
@@ -67,7 +72,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -77,113 +82,489 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9,800,000</t>
+          <t>15,800</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6,320,000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>커넥터 하우징</t>
+          <t>PCB 브라켓</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>411</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11,100,000</t>
+          <t>17,400</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7,160,000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>커넥터 하우징</t>
+          <t>PCB 브라켓</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>403</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13,700,000</t>
+          <t>18,700</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7,520,000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>실링 가스켓</t>
+          <t>실드 캔</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>414</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>15,600,000</t>
+          <t>17,600</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7,280,000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>커넥터 하우징</t>
+          <t>방열판</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>425</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18,400,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t>16,600</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7,040,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>실드 캔</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>21,500</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8,720,000</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>방열판</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20,300</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8,480,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>커넥터 하우징</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>19,300</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8,240,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PCB 브라켓</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>18,200</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>방열판</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>21,600</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8,840,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>커넥터 하우징</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>20,500</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8,600,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>커넥터 하우징</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>24,400</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>10,040,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PCB 브라켓</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>23,200</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>9,800,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>실드 캔</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>22,000</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>9,560,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PCB 브라켓</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>24,500</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>10,160,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>실드 캔</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>23,300</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>9,920,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>방열판</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>24,600</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>10,760,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>커넥터 하우징</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>25,800</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>10,520,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>합계금액</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>68,600,000</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>156,960,000</t>
         </is>
       </c>
     </row>

--- a/public/sample/거래명세서_한울전자_2026상반기.xlsx
+++ b/public/sample/거래명세서_한울전자_2026상반기.xlsx
@@ -20,549 +20,561 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>공급받는자</t>
+          <t>공급자</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>한울전자(주)</t>
+          <t>한빛정밀(주)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>공급받는자</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>한울전자(주)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>결제조건</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>검수 완료 후 익월 15일</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>거래일자</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>품목</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>단가</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>공급가액</t>
-        </is>
-      </c>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>거래일자</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>커넥터 하우징</t>
+          <t>품목</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>수량</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15,800</t>
+          <t>단가</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6,320,000</t>
+          <t>공급가액</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PCB 브라켓</t>
+          <t>센서 커넥터 하우징</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17,400</t>
+          <t>15,800</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7,160,000</t>
+          <t>6,320,000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PCB 브라켓</t>
+          <t>센서 브래킷</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>411</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18,700</t>
+          <t>17,400</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7,520,000</t>
+          <t>7,160,000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>실드 캔</t>
+          <t>센서 브래킷</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>403</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>17,600</t>
+          <t>18,700</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7,280,000</t>
+          <t>7,520,000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>방열판</t>
+          <t>하네스 어셈블리</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>414</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16,600</t>
+          <t>17,600</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7,040,000</t>
+          <t>7,280,000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>실드 캔</t>
+          <t>실링 캡</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>425</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>21,500</t>
+          <t>16,600</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8,720,000</t>
+          <t>7,040,000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>방열판</t>
+          <t>하네스 어셈블리</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>406</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20,300</t>
+          <t>21,500</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8,480,000</t>
+          <t>8,720,000</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>커넥터 하우징</t>
+          <t>실링 캡</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>417</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>19,300</t>
+          <t>20,300</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8,240,000</t>
+          <t>8,480,000</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PCB 브라켓</t>
+          <t>센서 커넥터 하우징</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>428</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>18,200</t>
+          <t>19,300</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>8,240,000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>방열판</t>
+          <t>센서 브래킷</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>439</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>21,600</t>
+          <t>18,200</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8,840,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>커넥터 하우징</t>
+          <t>실링 캡</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>409</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20,500</t>
+          <t>21,600</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8,600,000</t>
+          <t>8,840,000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>커넥터 하우징</t>
+          <t>센서 커넥터 하우징</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>420</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24,400</t>
+          <t>20,500</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10,040,000</t>
+          <t>8,600,000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PCB 브라켓</t>
+          <t>센서 커넥터 하우징</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>412</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>23,200</t>
+          <t>24,400</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9,800,000</t>
+          <t>10,040,000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>실드 캔</t>
+          <t>센서 브래킷</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>423</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>22,000</t>
+          <t>23,200</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9,560,000</t>
+          <t>9,800,000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PCB 브라켓</t>
+          <t>하네스 어셈블리</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>434</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>24,500</t>
+          <t>22,000</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10,160,000</t>
+          <t>9,560,000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>실드 캔</t>
+          <t>센서 브래킷</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>415</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>23,300</t>
+          <t>24,500</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>9,920,000</t>
+          <t>10,160,000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>방열판</t>
+          <t>하네스 어셈블리</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>426</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>24,600</t>
+          <t>23,300</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>10,760,000</t>
+          <t>9,920,000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>실링 캡</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>24,600</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>10,760,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>커넥터 하우징</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>센서 커넥터 하우징</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>408</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>25,800</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>10,520,000</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>합계금액</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>156,960,000</t>
         </is>

--- a/public/sample/거래명세서_한울전자_2026상반기.xlsx
+++ b/public/sample/거래명세서_한울전자_2026상반기.xlsx
@@ -20,561 +20,549 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>공급자</t>
+          <t>공급받는자</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>한빛정밀(주)</t>
+          <t>한울전자(주)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>공급받는자</t>
+          <t>결제조건</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>한울전자(주)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>결제조건</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t>검수 완료 후 익월 15일</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>거래일자</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>품목</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>단가</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>공급가액</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>거래일자</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>품목</t>
+          <t>커넥터 하우징</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>수량</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>단가</t>
+          <t>15,800</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>공급가액</t>
+          <t>6,320,000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>센서 커넥터 하우징</t>
+          <t>PCB 브라켓</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>411</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15,800</t>
+          <t>17,400</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6,320,000</t>
+          <t>7,160,000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>센서 브래킷</t>
+          <t>PCB 브라켓</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>403</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>17,400</t>
+          <t>18,700</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7,160,000</t>
+          <t>7,520,000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>센서 브래킷</t>
+          <t>실드 캔</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>414</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18,700</t>
+          <t>17,600</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7,520,000</t>
+          <t>7,280,000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>하네스 어셈블리</t>
+          <t>방열판</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>425</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>17,600</t>
+          <t>16,600</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7,280,000</t>
+          <t>7,040,000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>실링 캡</t>
+          <t>실드 캔</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>406</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16,600</t>
+          <t>21,500</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7,040,000</t>
+          <t>8,720,000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>하네스 어셈블리</t>
+          <t>방열판</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>417</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>21,500</t>
+          <t>20,300</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8,720,000</t>
+          <t>8,480,000</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>실링 캡</t>
+          <t>커넥터 하우징</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>428</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20,300</t>
+          <t>19,300</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8,480,000</t>
+          <t>8,240,000</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>센서 커넥터 하우징</t>
+          <t>PCB 브라켓</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>439</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19,300</t>
+          <t>18,200</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8,240,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>센서 브래킷</t>
+          <t>방열판</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>409</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18,200</t>
+          <t>21,600</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>8,840,000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>실링 캡</t>
+          <t>커넥터 하우징</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>420</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21,600</t>
+          <t>20,500</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8,840,000</t>
+          <t>8,600,000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>센서 커넥터 하우징</t>
+          <t>커넥터 하우징</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>412</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20,500</t>
+          <t>24,400</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8,600,000</t>
+          <t>10,040,000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>센서 커넥터 하우징</t>
+          <t>PCB 브라켓</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>423</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>24,400</t>
+          <t>23,200</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10,040,000</t>
+          <t>9,800,000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>센서 브래킷</t>
+          <t>실드 캔</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>434</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>23,200</t>
+          <t>22,000</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9,800,000</t>
+          <t>9,560,000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>하네스 어셈블리</t>
+          <t>PCB 브라켓</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>415</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>22,000</t>
+          <t>24,500</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9,560,000</t>
+          <t>10,160,000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>센서 브래킷</t>
+          <t>실드 캔</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>426</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>24,500</t>
+          <t>23,300</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>10,160,000</t>
+          <t>9,920,000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>하네스 어셈블리</t>
+          <t>방열판</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>23,300</t>
+          <t>24,600</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>9,920,000</t>
+          <t>10,760,000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>실링 캡</t>
+          <t>커넥터 하우징</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>408</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>24,600</t>
+          <t>25,800</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>10,760,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>센서 커넥터 하우징</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>25,800</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
           <t>10,520,000</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>합계금액</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>156,960,000</t>
         </is>
